--- a/data/BD.xlsx
+++ b/data/BD.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F8E5666-D546-442A-9C05-1EAAD4123CC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A2B5F4D-1362-43DC-8B4B-6E953D33B84D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{71813276-3BAA-4B65-95BD-377324816B62}"/>
   </bookViews>
@@ -928,6 +928,8 @@
   <dimension ref="A1:I51"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="2" width="35.28515625" customWidth="1"/>
+    <col min="3" max="3" width="32.85546875" customWidth="1"/>
     <col min="6" max="6" width="23.85546875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1000,7 +1002,7 @@
         <v>34</v>
       </c>
       <c r="D3">
-        <v>1605</v>
+        <v>1943</v>
       </c>
       <c r="E3">
         <v>9788491050296</v>
@@ -1029,7 +1031,7 @@
         <v>37</v>
       </c>
       <c r="D4">
-        <v>1872</v>
+        <v>1943</v>
       </c>
       <c r="E4">
         <v>9789500304023</v>
@@ -1058,7 +1060,7 @@
         <v>41</v>
       </c>
       <c r="D5">
-        <v>-800</v>
+        <v>1943</v>
       </c>
       <c r="E5">
         <v>9780140268867</v>
@@ -1087,7 +1089,7 @@
         <v>41</v>
       </c>
       <c r="D6">
-        <v>-750</v>
+        <v>1943</v>
       </c>
       <c r="E6">
         <v>9780140275360</v>
@@ -1116,7 +1118,7 @@
         <v>10</v>
       </c>
       <c r="D7">
-        <v>1949</v>
+        <v>1943</v>
       </c>
       <c r="E7">
         <v>9780451524935</v>
@@ -1145,7 +1147,7 @@
         <v>10</v>
       </c>
       <c r="D8">
-        <v>1945</v>
+        <v>1943</v>
       </c>
       <c r="E8">
         <v>9780451526342</v>
@@ -1174,7 +1176,7 @@
         <v>11</v>
       </c>
       <c r="D9">
-        <v>1967</v>
+        <v>1943</v>
       </c>
       <c r="E9">
         <v>9780307474728</v>
@@ -1203,7 +1205,7 @@
         <v>11</v>
       </c>
       <c r="D10">
-        <v>1981</v>
+        <v>1943</v>
       </c>
       <c r="E10">
         <v>9781400034710</v>
@@ -1232,7 +1234,7 @@
         <v>57</v>
       </c>
       <c r="D11">
-        <v>1948</v>
+        <v>1943</v>
       </c>
       <c r="E11">
         <v>9789500413947</v>
@@ -1261,7 +1263,7 @@
         <v>61</v>
       </c>
       <c r="D12">
-        <v>1953</v>
+        <v>1943</v>
       </c>
       <c r="E12">
         <v>9781451673319</v>
@@ -1290,7 +1292,7 @@
         <v>64</v>
       </c>
       <c r="D13">
-        <v>1915</v>
+        <v>1943</v>
       </c>
       <c r="E13">
         <v>9788491050203</v>
@@ -1319,7 +1321,7 @@
         <v>14</v>
       </c>
       <c r="D14">
-        <v>1963</v>
+        <v>1943</v>
       </c>
       <c r="E14">
         <v>9788437604572</v>
@@ -1348,7 +1350,7 @@
         <v>70</v>
       </c>
       <c r="D15">
-        <v>1918</v>
+        <v>1943</v>
       </c>
       <c r="E15">
         <v>9789871138456</v>
@@ -1377,7 +1379,7 @@
         <v>74</v>
       </c>
       <c r="D16">
-        <v>1838</v>
+        <v>1943</v>
       </c>
       <c r="E16">
         <v>9789875660212</v>
@@ -1406,7 +1408,7 @@
         <v>57</v>
       </c>
       <c r="D17">
-        <v>1961</v>
+        <v>1943</v>
       </c>
       <c r="E17">
         <v>9789500422505</v>
@@ -1435,7 +1437,7 @@
         <v>79</v>
       </c>
       <c r="D18">
-        <v>1982</v>
+        <v>1943</v>
       </c>
       <c r="E18">
         <v>9780553383805</v>
@@ -1464,7 +1466,7 @@
         <v>13</v>
       </c>
       <c r="D19">
-        <v>1949</v>
+        <v>1943</v>
       </c>
       <c r="E19">
         <v>9788420633122</v>
@@ -1493,7 +1495,7 @@
         <v>84</v>
       </c>
       <c r="D20">
-        <v>1947</v>
+        <v>1943</v>
       </c>
       <c r="E20">
         <v>9788497593063</v>
@@ -1522,7 +1524,7 @@
         <v>88</v>
       </c>
       <c r="D21">
-        <v>1949</v>
+        <v>1943</v>
       </c>
       <c r="E21">
         <v>9788437602134</v>
@@ -1551,7 +1553,7 @@
         <v>16</v>
       </c>
       <c r="D22">
-        <v>1603</v>
+        <v>1943</v>
       </c>
       <c r="E22">
         <v>9780743477123</v>
@@ -1580,7 +1582,7 @@
         <v>16</v>
       </c>
       <c r="D23">
-        <v>1597</v>
+        <v>1943</v>
       </c>
       <c r="E23">
         <v>9780743477116</v>
@@ -1609,7 +1611,7 @@
         <v>98</v>
       </c>
       <c r="D24">
-        <v>1554</v>
+        <v>1943</v>
       </c>
       <c r="E24">
         <v>9788420728422</v>
@@ -1638,7 +1640,7 @@
         <v>101</v>
       </c>
       <c r="D25">
-        <v>1499</v>
+        <v>1943</v>
       </c>
       <c r="E25">
         <v>9788420728293</v>
@@ -1667,7 +1669,7 @@
         <v>17</v>
       </c>
       <c r="D26">
-        <v>1818</v>
+        <v>1943</v>
       </c>
       <c r="E26">
         <v>9780486282114</v>
@@ -1696,7 +1698,7 @@
         <v>106</v>
       </c>
       <c r="D27">
-        <v>1897</v>
+        <v>1943</v>
       </c>
       <c r="E27">
         <v>9780486411095</v>
@@ -1725,7 +1727,7 @@
         <v>19</v>
       </c>
       <c r="D28">
-        <v>1813</v>
+        <v>1943</v>
       </c>
       <c r="E28">
         <v>9780141439518</v>
@@ -1754,7 +1756,7 @@
         <v>113</v>
       </c>
       <c r="D29">
-        <v>1851</v>
+        <v>1943</v>
       </c>
       <c r="E29">
         <v>9781503280786</v>
@@ -1783,7 +1785,7 @@
         <v>115</v>
       </c>
       <c r="D30">
-        <v>1890</v>
+        <v>1943</v>
       </c>
       <c r="E30">
         <v>9780141439570</v>
@@ -1812,7 +1814,7 @@
         <v>118</v>
       </c>
       <c r="D31">
-        <v>1883</v>
+        <v>1943</v>
       </c>
       <c r="E31">
         <v>9780141321004</v>
@@ -1841,7 +1843,7 @@
         <v>121</v>
       </c>
       <c r="D32">
-        <v>1864</v>
+        <v>1943</v>
       </c>
       <c r="E32">
         <v>9788420726626</v>
@@ -1870,7 +1872,7 @@
         <v>121</v>
       </c>
       <c r="D33">
-        <v>1870</v>
+        <v>1943</v>
       </c>
       <c r="E33">
         <v>9788420726671</v>
@@ -1899,7 +1901,7 @@
         <v>126</v>
       </c>
       <c r="D34">
-        <v>1859</v>
+        <v>1943</v>
       </c>
       <c r="E34">
         <v>9781503253780</v>
@@ -1928,7 +1930,7 @@
         <v>21</v>
       </c>
       <c r="D35">
-        <v>1988</v>
+        <v>1943</v>
       </c>
       <c r="E35">
         <v>9780553380163</v>
@@ -1957,7 +1959,7 @@
         <v>23</v>
       </c>
       <c r="D36">
-        <v>1980</v>
+        <v>1943</v>
       </c>
       <c r="E36">
         <v>9780345539434</v>
@@ -1986,7 +1988,7 @@
         <v>134</v>
       </c>
       <c r="D37">
-        <v>1976</v>
+        <v>1943</v>
       </c>
       <c r="E37">
         <v>9780199291151</v>
@@ -2015,7 +2017,7 @@
         <v>25</v>
       </c>
       <c r="D38">
-        <v>2011</v>
+        <v>1943</v>
       </c>
       <c r="E38">
         <v>9780062316097</v>
@@ -2044,7 +2046,7 @@
         <v>25</v>
       </c>
       <c r="D39">
-        <v>2015</v>
+        <v>1943</v>
       </c>
       <c r="E39">
         <v>9780062464316</v>
@@ -2073,7 +2075,7 @@
         <v>141</v>
       </c>
       <c r="D40">
-        <v>1991</v>
+        <v>1943</v>
       </c>
       <c r="E40">
         <v>9788434411616</v>
@@ -2102,7 +2104,7 @@
         <v>144</v>
       </c>
       <c r="D41">
-        <v>1991</v>
+        <v>1943</v>
       </c>
       <c r="E41">
         <v>9788478448159</v>
@@ -2131,7 +2133,7 @@
         <v>148</v>
       </c>
       <c r="D42">
-        <v>-380</v>
+        <v>1943</v>
       </c>
       <c r="E42">
         <v>9788420674200</v>
@@ -2160,7 +2162,7 @@
         <v>151</v>
       </c>
       <c r="D43">
-        <v>1762</v>
+        <v>1943</v>
       </c>
       <c r="E43">
         <v>9788420674217</v>
@@ -2189,7 +2191,7 @@
         <v>154</v>
       </c>
       <c r="D44">
-        <v>1532</v>
+        <v>1943</v>
       </c>
       <c r="E44">
         <v>9788420674224</v>
@@ -2218,7 +2220,7 @@
         <v>157</v>
       </c>
       <c r="D45">
-        <v>1689</v>
+        <v>1943</v>
       </c>
       <c r="E45">
         <v>9788420674231</v>
@@ -2247,7 +2249,7 @@
         <v>161</v>
       </c>
       <c r="D46">
-        <v>1867</v>
+        <v>1943</v>
       </c>
       <c r="E46">
         <v>9788420674248</v>
@@ -2276,7 +2278,7 @@
         <v>165</v>
       </c>
       <c r="D47">
-        <v>1776</v>
+        <v>1943</v>
       </c>
       <c r="E47">
         <v>9788420674255</v>
@@ -2305,7 +2307,7 @@
         <v>169</v>
       </c>
       <c r="D48">
-        <v>2005</v>
+        <v>1943</v>
       </c>
       <c r="E48">
         <v>9789500730020</v>
@@ -2334,7 +2336,7 @@
         <v>173</v>
       </c>
       <c r="D49">
-        <v>1957</v>
+        <v>1943</v>
       </c>
       <c r="E49">
         <v>9789500429016</v>
@@ -2363,7 +2365,7 @@
         <v>177</v>
       </c>
       <c r="D50">
-        <v>1984</v>
+        <v>1943</v>
       </c>
       <c r="E50">
         <v>9789875660045</v>
@@ -2392,7 +2394,7 @@
         <v>181</v>
       </c>
       <c r="D51">
-        <v>2006</v>
+        <v>1943</v>
       </c>
       <c r="E51">
         <v>9788498380792</v>
